--- a/parolIKV2.xlsx
+++ b/parolIKV2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fudayl/git/my_robot/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A8207410-E547-CD40-B522-7DCC0D228C76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2277034F-827F-954F-9FA4-250ED2705521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="34400" windowHeight="26620" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34400" yWindow="600" windowWidth="34400" windowHeight="28200" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Export Summary" sheetId="1" r:id="rId1"/>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="L6" s="11" cm="1">
         <f t="array" ref="L6">D16</f>
-        <v>1.5707963267948966</v>
+        <v>0</v>
       </c>
       <c r="M6" s="11">
         <v>176.35</v>
@@ -2380,7 +2380,7 @@
       <c r="AA6" s="13"/>
       <c r="AB6" s="12" cm="1">
         <f t="array" ref="AB6">D16</f>
-        <v>1.5707963267948966</v>
+        <v>0</v>
       </c>
       <c r="AC6" s="12">
         <v>-176.35</v>
@@ -2433,7 +2433,7 @@
       </c>
       <c r="L7" s="11" cm="1">
         <f t="array" ref="L7">D17</f>
-        <v>-1.1170107212763709</v>
+        <v>0</v>
       </c>
       <c r="M7" s="11">
         <v>0</v>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="AB7" s="12" cm="1">
         <f t="array" ref="AB7">D17</f>
-        <v>-1.1170107212763709</v>
+        <v>0</v>
       </c>
       <c r="AC7" s="12">
         <v>0</v>
@@ -3025,11 +3025,11 @@
         <v>30</v>
       </c>
       <c r="C16" s="20">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D16" s="21" cm="1">
         <f t="array" ref="D16">RADIANS(C16)</f>
-        <v>1.5707963267948966</v>
+        <v>0</v>
       </c>
       <c r="E16" s="8"/>
       <c r="F16" s="8"/>
@@ -3117,11 +3117,11 @@
         <v>32</v>
       </c>
       <c r="C17" s="20">
-        <v>-64</v>
+        <v>0</v>
       </c>
       <c r="D17" s="21" cm="1">
         <f t="array" ref="D17">RADIANS(C17)</f>
-        <v>-1.1170107212763709</v>
+        <v>0</v>
       </c>
       <c r="E17" s="8"/>
       <c r="F17" s="8"/>
@@ -3425,11 +3425,11 @@
       </c>
       <c r="C21" s="28" cm="1">
         <f t="array" ref="C21">R47</f>
-        <v>-89.879404629916664</v>
+        <v>2.6857440500091989E-14</v>
       </c>
       <c r="D21" s="28" cm="1">
         <f t="array" ref="D21">AH41</f>
-        <v>279.07283040314246</v>
+        <v>334.38156826091523</v>
       </c>
       <c r="E21" s="28" cm="1">
         <f t="array" ref="E21">IF(ABS(C21-D21)&lt;0.1,1,0)</f>
@@ -3506,11 +3506,11 @@
       </c>
       <c r="C22" s="28" cm="1">
         <f t="array" ref="C22">R48</f>
-        <v>292.36935804260526</v>
+        <v>282.61675727917168</v>
       </c>
       <c r="D22" s="28" cm="1">
         <f t="array" ref="D22">AH42</f>
-        <v>-89.879404629916721</v>
+        <v>-2.7459575503791794E-14</v>
       </c>
       <c r="E22" s="28" cm="1">
         <f t="array" ref="E22">IF(ABS(C22-D22)&lt;0.1,1,0)</f>
@@ -3580,11 +3580,11 @@
       </c>
       <c r="C23" s="28" cm="1">
         <f t="array" ref="C23">R49</f>
-        <v>279.07240479172719</v>
+        <v>334.38204650037716</v>
       </c>
       <c r="D23" s="28" cm="1">
         <f t="array" ref="D23">AH43</f>
-        <v>292.34856695806133</v>
+        <v>282.59084159964209</v>
       </c>
       <c r="E23" s="28" cm="1">
         <f t="array" ref="E23">IF(ABS(C23-D23)&lt;0.1,1,0)</f>
@@ -3660,11 +3660,11 @@
       </c>
       <c r="C24" s="28" cm="1">
         <f t="array" ref="C24">DEGREES(C27)</f>
-        <v>-63.999999999999986</v>
+        <v>10.000018723968342</v>
       </c>
       <c r="D24" s="28" cm="1">
         <f t="array" ref="D24">DEGREES(D27)</f>
-        <v>26.347179045797283</v>
+        <v>-3.0555237504089516E-2</v>
       </c>
       <c r="E24" s="8"/>
       <c r="G24" s="8"/>
@@ -3730,11 +3730,11 @@
       </c>
       <c r="C25" s="28" cm="1">
         <f t="array" ref="C25">DEGREES(C28)</f>
-        <v>-10.00001872396834</v>
+        <v>6.3541887885436076E-15</v>
       </c>
       <c r="D25" s="28" cm="1">
         <f t="array" ref="D25">DEGREES(D28)</f>
-        <v>8.9785681500312382</v>
+        <v>-79.994671222381413</v>
       </c>
       <c r="E25" s="8"/>
       <c r="G25" s="6"/>
@@ -3827,11 +3827,11 @@
       </c>
       <c r="C26" s="28" cm="1">
         <f t="array" ref="C26">DEGREES(C29)</f>
-        <v>90</v>
+        <v>7.5726298296413201E-15</v>
       </c>
       <c r="D26" s="28" cm="1">
         <f t="array" ref="D26">DEGREES(D29)</f>
-        <v>-9.0049402725160377</v>
+        <v>90.005308659651874</v>
       </c>
       <c r="E26" s="8"/>
       <c r="G26" s="6"/>
@@ -3921,11 +3921,11 @@
       </c>
       <c r="C27" s="28">
         <f>ATAN2(Q49,P49)</f>
-        <v>-1.1170107212763707</v>
+        <v>0.17453325199432956</v>
       </c>
       <c r="D27" s="28" cm="1">
         <f t="array" ref="D27">ATAN2(AE41/COS(D28),AE42/COS(D28))</f>
-        <v>0.45984502296162044</v>
+        <v>-5.3328949817521641E-4</v>
       </c>
       <c r="E27" s="8"/>
       <c r="F27" s="8"/>
@@ -3999,11 +3999,11 @@
       </c>
       <c r="C28" s="28">
         <f>ATAN2((P49^2+Q49^2)^0.5,-O49)</f>
-        <v>-0.17453325199432954</v>
+        <v>1.109015156533957E-16</v>
       </c>
       <c r="D28" s="28" cm="1">
         <f t="array" ref="D28">ATAN2((AF43^2+AG43^2)^0.5,-AE43)</f>
-        <v>0.15670557633274132</v>
+        <v>-1.3961703968809127</v>
       </c>
       <c r="E28" s="8"/>
       <c r="F28" s="8"/>
@@ -4070,11 +4070,11 @@
       </c>
       <c r="C29" s="28">
         <f>ATAN2(O47,O48)</f>
-        <v>1.5707963267948966</v>
+        <v>1.3216732356197833E-16</v>
       </c>
       <c r="D29" s="28" cm="1">
         <f t="array" ref="D29">ATAN2(AF43/COS(D28),AE43/COS(D28))</f>
-        <v>-0.1571658567008403</v>
+        <v>1.5708889803846895</v>
       </c>
       <c r="E29" s="8"/>
       <c r="G29" s="8"/>
@@ -4089,10 +4089,10 @@
       </c>
       <c r="O29" s="12" cm="1">
         <f t="array" ref="O29:R32">MMULT(_xlfn.ANCHORARRAY(O23),I31:L34)</f>
+        <v>-4.9669175696028064E-17</v>
+      </c>
+      <c r="P29" s="12">
         <v>-1</v>
-      </c>
-      <c r="P29" s="12">
-        <v>-1.1563164261339596E-17</v>
       </c>
       <c r="Q29" s="12">
         <v>1.3216732356197833E-16</v>
@@ -4116,13 +4116,13 @@
       </c>
       <c r="AE29" s="12" cm="1">
         <f t="array" ref="AE29:AH32">MMULT(_xlfn.ANCHORARRAY(AE23),Y31:AB34)</f>
-        <v>-7.0941556198671339E-17</v>
+        <v>-0.17373974471989401</v>
       </c>
       <c r="AF29" s="12">
         <v>0.98479160288086642</v>
       </c>
       <c r="AG29" s="12">
-        <v>0.17373974471989395</v>
+        <v>-1.2060415930063873E-16</v>
       </c>
       <c r="AH29" s="12">
         <v>235.90240797282857</v>
@@ -4154,10 +4154,10 @@
       <c r="M30" s="6"/>
       <c r="N30" s="33"/>
       <c r="O30" s="12">
-        <v>-1.1563164261339602E-17</v>
+        <v>0.98480769626481723</v>
       </c>
       <c r="P30" s="12">
-        <v>-0.98480769626481723</v>
+        <v>-7.1865243911658964E-17</v>
       </c>
       <c r="Q30" s="12">
         <v>-0.1736484994970689</v>
@@ -4178,13 +4178,13 @@
       <c r="AC30" s="6"/>
       <c r="AD30" s="33"/>
       <c r="AE30" s="12">
+        <v>6.0312441006962954E-17</v>
+      </c>
+      <c r="AF30" s="12">
+        <v>-1.1182618827627998E-16</v>
+      </c>
+      <c r="AG30" s="12">
         <v>-1</v>
-      </c>
-      <c r="AF30" s="12">
-        <v>-5.0593848318912331E-17</v>
-      </c>
-      <c r="AG30" s="12">
-        <v>-1.2154478096433061E-16</v>
       </c>
       <c r="AH30" s="12">
         <v>-2.2400190671900561E-14</v>
@@ -4213,11 +4213,11 @@
       </c>
       <c r="I31" s="12" cm="1">
         <f t="array" ref="I31">COS(L6)</f>
-        <v>6.123233995736766E-17</v>
+        <v>1</v>
       </c>
       <c r="J31" s="12" cm="1">
         <f t="array" ref="J31">-SIN(L6)</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K31" s="12">
         <v>0</v>
@@ -4229,10 +4229,10 @@
       <c r="M31" s="22"/>
       <c r="N31" s="33"/>
       <c r="O31" s="12">
-        <v>1.3216732356197833E-16</v>
+        <v>0.1736484994970689</v>
       </c>
       <c r="P31" s="12">
-        <v>-0.1736484994970689</v>
+        <v>1.2153441960768702E-16</v>
       </c>
       <c r="Q31" s="12">
         <v>0.98480769626481723</v>
@@ -4250,15 +4250,15 @@
       </c>
       <c r="Y31" s="12" cm="1">
         <f t="array" ref="Y31">COS(AB6)</f>
-        <v>6.123233995736766E-17</v>
+        <v>1</v>
       </c>
       <c r="Z31" s="12" cm="1">
         <f t="array" ref="Z31">-SIN(AB6)*COS(Z6)</f>
-        <v>-6.123233995736766E-17</v>
+        <v>0</v>
       </c>
       <c r="AA31" s="12" cm="1">
         <f t="array" ref="AA31">SIN(AB6)*SIN(Z6)</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AB31" s="12" cm="1">
         <f t="array" ref="AB31">AA6*COS(AB6)</f>
@@ -4267,13 +4267,13 @@
       <c r="AC31" s="22"/>
       <c r="AD31" s="33"/>
       <c r="AE31" s="12">
-        <v>-1.1090611737634209E-16</v>
+        <v>-0.98479160288086642</v>
       </c>
       <c r="AF31" s="12">
-        <v>-0.17373974471989395</v>
+        <v>-0.17373974471989401</v>
       </c>
       <c r="AG31" s="12">
-        <v>0.98479160288086642</v>
+        <v>-3.9966532048785048E-17</v>
       </c>
       <c r="AH31" s="12">
         <v>299.9648160716315</v>
@@ -4301,11 +4301,11 @@
       <c r="H32" s="36"/>
       <c r="I32" s="12" cm="1">
         <f t="array" ref="I32">SIN(L6)*COS(J6)</f>
-        <v>6.123233995736766E-17</v>
+        <v>0</v>
       </c>
       <c r="J32" s="12" cm="1">
         <f t="array" ref="J32">COS(L6)*COS(J6)</f>
-        <v>3.749399456654644E-33</v>
+        <v>6.123233995736766E-17</v>
       </c>
       <c r="K32" s="12" cm="1">
         <f t="array" ref="K32">-SIN(J6)</f>
@@ -4337,15 +4337,15 @@
       <c r="X32" s="36"/>
       <c r="Y32" s="12" cm="1">
         <f t="array" ref="Y32">SIN(AB6)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z32" s="12" cm="1">
         <f t="array" ref="Z32">COS(AB6)*COS(Z6)</f>
-        <v>3.749399456654644E-33</v>
+        <v>6.123233995736766E-17</v>
       </c>
       <c r="AA32" s="12" cm="1">
         <f t="array" ref="AA32">-COS(AB6)*SIN(Z6)</f>
-        <v>6.123233995736766E-17</v>
+        <v>1</v>
       </c>
       <c r="AB32" s="12" cm="1">
         <f t="array" ref="AB32">AA6*SIN(AB6)</f>
@@ -4388,11 +4388,11 @@
       <c r="H33" s="36"/>
       <c r="I33" s="12" cm="1">
         <f t="array" ref="I33">SIN(L6)*SIN(J6)</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J33" s="12" cm="1">
         <f t="array" ref="J33">COS(L6)*SIN(J6)</f>
-        <v>-6.123233995736766E-17</v>
+        <v>-1</v>
       </c>
       <c r="K33" s="12" cm="1">
         <f t="array" ref="K33">COS(J6)</f>
@@ -4529,13 +4529,13 @@
       </c>
       <c r="O35" s="12" cm="1">
         <f t="array" ref="O35:R38">MMULT(_xlfn.ANCHORARRAY(O29),I37:L40)</f>
-        <v>-0.43837114678907757</v>
+        <v>-4.9669175696028064E-17</v>
       </c>
       <c r="P35" s="12">
-        <v>-0.89879404629916682</v>
+        <v>7.0934983604610671E-17</v>
       </c>
       <c r="Q35" s="12">
-        <v>1.1563164261339604E-17</v>
+        <v>1</v>
       </c>
       <c r="R35" s="12">
         <v>1.3640708143894156E-14</v>
@@ -4556,13 +4556,13 @@
       </c>
       <c r="AE35" s="12" cm="1">
         <f t="array" ref="AE35:AH38">MMULT(_xlfn.ANCHORARRAY(AE29),Y37:AB40)</f>
-        <v>-0.88512482951473626</v>
+        <v>-0.17373974471989401</v>
       </c>
       <c r="AF35" s="12">
-        <v>0.17373974471989398</v>
+        <v>-6.0303065085876511E-17</v>
       </c>
       <c r="AG35" s="12">
-        <v>-0.43170422430313909</v>
+        <v>-0.98479160288086642</v>
       </c>
       <c r="AH35" s="12">
         <v>235.90240797282857</v>
@@ -4595,13 +4595,13 @@
       <c r="M36" s="6"/>
       <c r="N36" s="33"/>
       <c r="O36" s="12">
-        <v>0.15607423749674945</v>
+        <v>0.98480769626481723</v>
       </c>
       <c r="P36" s="12">
-        <v>-7.6122491862732677E-2</v>
+        <v>-0.1736484994970689</v>
       </c>
       <c r="Q36" s="12">
-        <v>0.98480769626481723</v>
+        <v>6.1232339957367648E-17</v>
       </c>
       <c r="R36" s="12">
         <v>299.98160722887854</v>
@@ -4619,13 +4619,13 @@
       <c r="AC36" s="6"/>
       <c r="AD36" s="33"/>
       <c r="AE36" s="12">
-        <v>-0.4383711467890774</v>
+        <v>6.0312441006962954E-17</v>
       </c>
       <c r="AF36" s="12">
-        <v>-1.7658004355897925E-16</v>
+        <v>-1</v>
       </c>
       <c r="AG36" s="12">
-        <v>0.89879404629916693</v>
+        <v>5.0593848318912324E-17</v>
       </c>
       <c r="AH36" s="12">
         <v>-2.2400190671900561E-14</v>
@@ -4655,11 +4655,11 @@
       </c>
       <c r="I37" s="12" cm="1">
         <f t="array" ref="I37">COS(L7)</f>
-        <v>0.43837114678907746</v>
+        <v>1</v>
       </c>
       <c r="J37" s="12" cm="1">
         <f t="array" ref="J37">-SIN(L7)</f>
-        <v>0.89879404629916693</v>
+        <v>0</v>
       </c>
       <c r="K37" s="12">
         <v>0</v>
@@ -4671,13 +4671,13 @@
       <c r="M37" s="22"/>
       <c r="N37" s="33"/>
       <c r="O37" s="12">
-        <v>-0.88513929415241599</v>
+        <v>0.1736484994970689</v>
       </c>
       <c r="P37" s="12">
-        <v>0.43171127917831753</v>
+        <v>0.98480769626481723</v>
       </c>
       <c r="Q37" s="12">
-        <v>0.17364849949706895</v>
+        <v>-6.1232339957367648E-17</v>
       </c>
       <c r="R37" s="12">
         <v>235.90127687389543</v>
@@ -4692,15 +4692,15 @@
       </c>
       <c r="Y37" s="12" cm="1">
         <f t="array" ref="Y37">COS(AB7)</f>
-        <v>0.43837114678907746</v>
+        <v>1</v>
       </c>
       <c r="Z37" s="12" cm="1">
         <f t="array" ref="Z37">-SIN(AB7)*COS(Z7)</f>
-        <v>5.503526259464864E-17</v>
+        <v>0</v>
       </c>
       <c r="AA37" s="12" cm="1">
         <f t="array" ref="AA37">SIN(AB7)*SIN(Z7)</f>
-        <v>-0.89879404629916693</v>
+        <v>0</v>
       </c>
       <c r="AB37" s="12" cm="1">
         <f t="array" ref="AB37">AA7*COS(AB7)</f>
@@ -4709,13 +4709,13 @@
       <c r="AC37" s="22"/>
       <c r="AD37" s="33"/>
       <c r="AE37" s="12">
-        <v>0.15615624815977774</v>
+        <v>-0.98479160288086642</v>
       </c>
       <c r="AF37" s="12">
-        <v>0.98479160288086642</v>
+        <v>-5.0605023161579869E-17</v>
       </c>
       <c r="AG37" s="12">
-        <v>7.6162491135701629E-2</v>
+        <v>0.17373974471989401</v>
       </c>
       <c r="AH37" s="12">
         <v>299.9648160716315</v>
@@ -4743,11 +4743,11 @@
       <c r="H38" s="36"/>
       <c r="I38" s="12" cm="1">
         <f t="array" ref="I38">SIN(L7)*COS(J7)</f>
-        <v>-5.503526259464864E-17</v>
+        <v>0</v>
       </c>
       <c r="J38" s="12" cm="1">
         <f t="array" ref="J38">COS(L7)*COS(J7)</f>
-        <v>2.6842491087689912E-17</v>
+        <v>6.123233995736766E-17</v>
       </c>
       <c r="K38" s="12" cm="1">
         <f t="array" ref="K38">-SIN(J7)</f>
@@ -4779,15 +4779,15 @@
       <c r="X38" s="36"/>
       <c r="Y38" s="12" cm="1">
         <f t="array" ref="Y38">SIN(AB7)</f>
-        <v>-0.89879404629916693</v>
+        <v>0</v>
       </c>
       <c r="Z38" s="12" cm="1">
         <f t="array" ref="Z38">COS(AB7)*COS(Z7)</f>
-        <v>2.6842491087689912E-17</v>
+        <v>6.123233995736766E-17</v>
       </c>
       <c r="AA38" s="12" cm="1">
         <f t="array" ref="AA38">-COS(AB7)*SIN(Z7)</f>
-        <v>-0.43837114678907746</v>
+        <v>-1</v>
       </c>
       <c r="AB38" s="12" cm="1">
         <f t="array" ref="AB38">AA7*SIN(AB7)</f>
@@ -4830,11 +4830,11 @@
       <c r="H39" s="36"/>
       <c r="I39" s="12" cm="1">
         <f t="array" ref="I39">SIN(L7)*SIN(J7)</f>
-        <v>-0.89879404629916693</v>
+        <v>0</v>
       </c>
       <c r="J39" s="12" cm="1">
         <f t="array" ref="J39">COS(L7)*SIN(J7)</f>
-        <v>0.43837114678907746</v>
+        <v>1</v>
       </c>
       <c r="K39" s="12" cm="1">
         <f t="array" ref="K39">COS(J7)</f>
@@ -4971,13 +4971,13 @@
       </c>
       <c r="O41" s="12" cm="1">
         <f t="array" ref="O41:R44">MMULT(_xlfn.ANCHORARRAY(O35),I43:L46)</f>
-        <v>-0.43837114678907757</v>
+        <v>-4.9669175696028064E-17</v>
       </c>
       <c r="P41" s="12">
-        <v>-6.6598426855988242E-17</v>
+        <v>-1</v>
       </c>
       <c r="Q41" s="12">
-        <v>-0.89879404629916682</v>
+        <v>1.3216732356197833E-16</v>
       </c>
       <c r="R41" s="12">
         <v>1.3640708143894156E-14</v>
@@ -4998,16 +4998,16 @@
       </c>
       <c r="AE41" s="12" cm="1">
         <f t="array" ref="AE41:AH44">MMULT(_xlfn.ANCHORARRAY(AE35),Y43:AB46)</f>
-        <v>0.88514092332649108</v>
+        <v>0.1737397439741433</v>
       </c>
       <c r="AF41" s="12">
-        <v>0.17365773398139103</v>
+        <v>-1.6097611015176289E-5</v>
       </c>
       <c r="AG41" s="12">
-        <v>0.43170422430313909</v>
+        <v>0.98479160288086642</v>
       </c>
       <c r="AH41" s="12">
-        <v>279.07283040314246</v>
+        <v>334.38156826091523</v>
       </c>
       <c r="AI41" s="7"/>
       <c r="AJ41" s="8"/>
@@ -5037,13 +5037,13 @@
       <c r="M42" s="6"/>
       <c r="N42" s="33"/>
       <c r="O42" s="12">
-        <v>0.15607423749674945</v>
+        <v>0.98480769626481723</v>
       </c>
       <c r="P42" s="12">
-        <v>-0.98480769626481723</v>
+        <v>-7.1865243911658964E-17</v>
       </c>
       <c r="Q42" s="12">
-        <v>-7.6122491862732622E-2</v>
+        <v>-0.1736484994970689</v>
       </c>
       <c r="R42" s="12">
         <v>299.98160722887854</v>
@@ -5061,16 +5061,16 @@
       <c r="AC42" s="6"/>
       <c r="AD42" s="33"/>
       <c r="AE42" s="12">
-        <v>0.43837114490743773</v>
+        <v>-9.2653589660550567E-5</v>
       </c>
       <c r="AF42" s="12">
-        <v>-4.0616660353660227E-5</v>
+        <v>-0.99999999570765619</v>
       </c>
       <c r="AG42" s="12">
-        <v>-0.89879404629916693</v>
+        <v>-1.7305852770798714E-16</v>
       </c>
       <c r="AH42" s="12">
-        <v>-89.879404629916721</v>
+        <v>-2.7459575503791794E-14</v>
       </c>
       <c r="AI42" s="7"/>
       <c r="AJ42" s="8"/>
@@ -5113,13 +5113,13 @@
       <c r="M43" s="22"/>
       <c r="N43" s="33"/>
       <c r="O43" s="12">
-        <v>-0.88513929415241599</v>
+        <v>0.1736484994970689</v>
       </c>
       <c r="P43" s="12">
-        <v>-0.17364849949706893</v>
+        <v>1.2153441960768702E-16</v>
       </c>
       <c r="Q43" s="12">
-        <v>0.43171127917831753</v>
+        <v>0.98480769626481723</v>
       </c>
       <c r="R43" s="12">
         <v>235.90127687389543</v>
@@ -5151,16 +5151,16 @@
       <c r="AC43" s="22"/>
       <c r="AD43" s="33"/>
       <c r="AE43" s="12">
-        <v>-0.15606500301242701</v>
+        <v>0.98479159865380228</v>
       </c>
       <c r="AF43" s="12">
-        <v>0.98480606709074214</v>
+        <v>-9.1244477074449602E-5</v>
       </c>
       <c r="AG43" s="12">
-        <v>-7.6162491135701504E-2</v>
+        <v>-0.17373974471989401</v>
       </c>
       <c r="AH43" s="12">
-        <v>292.34856695806133</v>
+        <v>282.59084159964209</v>
       </c>
       <c r="AI43" s="7"/>
       <c r="AJ43" s="8"/>
@@ -5413,16 +5413,16 @@
       </c>
       <c r="O47" s="12" cm="1">
         <f t="array" ref="O47:R50">MMULT(_xlfn.ANCHORARRAY(O41),I49:L52)</f>
-        <v>3.9755935768298324E-17</v>
+        <v>1</v>
       </c>
       <c r="P47" s="12">
-        <v>-0.43837114678907757</v>
+        <v>-1.1090151565339572E-16</v>
       </c>
       <c r="Q47" s="12">
-        <v>-0.89879404629916682</v>
+        <v>1.3216732356197833E-16</v>
       </c>
       <c r="R47" s="12">
-        <v>-89.879404629916664</v>
+        <v>2.6857440500091989E-14</v>
       </c>
       <c r="S47" s="7"/>
       <c r="T47" s="8"/>
@@ -5468,16 +5468,16 @@
       <c r="M48" s="6"/>
       <c r="N48" s="33"/>
       <c r="O48" s="12">
+        <v>1.3216732356197833E-16</v>
+      </c>
+      <c r="P48" s="12">
         <v>0.98480769626481723</v>
       </c>
-      <c r="P48" s="12">
-        <v>0.1560742374967494</v>
-      </c>
       <c r="Q48" s="12">
-        <v>-7.6122491862732622E-2</v>
+        <v>-0.1736484994970689</v>
       </c>
       <c r="R48" s="12">
-        <v>292.36935804260526</v>
+        <v>282.61675727917168</v>
       </c>
       <c r="S48" s="7"/>
       <c r="T48" s="8"/>
@@ -5536,16 +5536,16 @@
       <c r="M49" s="22"/>
       <c r="N49" s="33"/>
       <c r="O49" s="12">
-        <v>0.17364849949706887</v>
+        <v>-1.109015156533957E-16</v>
       </c>
       <c r="P49" s="12">
-        <v>-0.88513929415241599</v>
+        <v>0.1736484994970689</v>
       </c>
       <c r="Q49" s="12">
-        <v>0.43171127917831753</v>
+        <v>0.98480769626481723</v>
       </c>
       <c r="R49" s="12">
-        <v>279.07240479172719</v>
+        <v>334.38204650037716</v>
       </c>
       <c r="S49" s="7"/>
       <c r="T49" s="8"/>

--- a/parolIKV2.xlsx
+++ b/parolIKV2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fudayl/git/my_robot/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2277034F-827F-954F-9FA4-250ED2705521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{034D7E55-DCC1-C348-BEC5-1142FE0E3B7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34400" yWindow="600" windowWidth="34400" windowHeight="28200" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="21200" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Export Summary" sheetId="1" r:id="rId1"/>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="L5" s="11" cm="1">
         <f t="array" ref="L5">D15</f>
-        <v>0</v>
+        <v>0.31415926535897931</v>
       </c>
       <c r="M5" s="11">
         <v>0</v>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="AB5" s="12" cm="1">
         <f t="array" ref="AB5">D15+3.1415</f>
-        <v>3.1415000000000002</v>
+        <v>3.4556592653589795</v>
       </c>
       <c r="AC5" s="12">
         <v>0</v>
@@ -2433,7 +2433,7 @@
       </c>
       <c r="L7" s="11" cm="1">
         <f t="array" ref="L7">D17</f>
-        <v>0</v>
+        <v>-0.50143309409797088</v>
       </c>
       <c r="M7" s="11">
         <v>0</v>
@@ -2461,7 +2461,7 @@
       </c>
       <c r="AB7" s="12" cm="1">
         <f t="array" ref="AB7">D17</f>
-        <v>0</v>
+        <v>-0.50143309409797088</v>
       </c>
       <c r="AC7" s="12">
         <v>0</v>
@@ -2948,11 +2948,11 @@
         <v>29</v>
       </c>
       <c r="C15" s="20">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D15" s="21" cm="1">
         <f t="array" ref="D15">RADIANS(C15)</f>
-        <v>0</v>
+        <v>0.31415926535897931</v>
       </c>
       <c r="E15" s="8"/>
       <c r="F15" s="8"/>
@@ -3117,11 +3117,11 @@
         <v>32</v>
       </c>
       <c r="C17" s="20">
-        <v>0</v>
+        <v>-28.73</v>
       </c>
       <c r="D17" s="21" cm="1">
         <f t="array" ref="D17">RADIANS(C17)</f>
-        <v>0</v>
+        <v>-0.50143309409797088</v>
       </c>
       <c r="E17" s="8"/>
       <c r="F17" s="8"/>
@@ -3425,11 +3425,11 @@
       </c>
       <c r="C21" s="28" cm="1">
         <f t="array" ref="C21">R47</f>
-        <v>2.6857440500091989E-14</v>
+        <v>2.8962416690160015E-14</v>
       </c>
       <c r="D21" s="28" cm="1">
         <f t="array" ref="D21">AH41</f>
-        <v>334.38156826091523</v>
+        <v>316.78535131080059</v>
       </c>
       <c r="E21" s="28" cm="1">
         <f t="array" ref="E21">IF(ABS(C21-D21)&lt;0.1,1,0)</f>
@@ -3506,11 +3506,11 @@
       </c>
       <c r="C22" s="28" cm="1">
         <f t="array" ref="C22">R48</f>
-        <v>282.61675727917168</v>
+        <v>244.65626116816583</v>
       </c>
       <c r="D22" s="28" cm="1">
         <f t="array" ref="D22">AH42</f>
-        <v>-2.7459575503791794E-14</v>
+        <v>-2.6831089774915E-14</v>
       </c>
       <c r="E22" s="28" cm="1">
         <f t="array" ref="E22">IF(ABS(C22-D22)&lt;0.1,1,0)</f>
@@ -3580,11 +3580,11 @@
       </c>
       <c r="C23" s="28" cm="1">
         <f t="array" ref="C23">R49</f>
-        <v>334.38204650037716</v>
+        <v>330.7984203821494</v>
       </c>
       <c r="D23" s="28" cm="1">
         <f t="array" ref="D23">AH43</f>
-        <v>282.59084159964209</v>
+        <v>319.96439258575617</v>
       </c>
       <c r="E23" s="28" cm="1">
         <f t="array" ref="E23">IF(ABS(C23-D23)&lt;0.1,1,0)</f>
@@ -3603,10 +3603,10 @@
       </c>
       <c r="O23" s="12" cm="1">
         <f t="array" ref="O23:R26">MMULT(_xlfn.ANCHORARRAY(O16),I25:L28)</f>
-        <v>-4.9669175696028064E-17</v>
+        <v>-2.5318077775183396E-17</v>
       </c>
       <c r="P23" s="12">
-        <v>7.0934983604610671E-17</v>
+        <v>8.2811797777122638E-17</v>
       </c>
       <c r="Q23" s="12">
         <v>1</v>
@@ -3630,16 +3630,16 @@
       </c>
       <c r="AE23" s="12" cm="1">
         <f t="array" ref="AE23:AH26">MMULT(_xlfn.ANCHORARRAY(AE16),Y25:AB28)</f>
-        <v>-0.17373974471989401</v>
+        <v>0.13908102485262044</v>
       </c>
       <c r="AF23" s="12">
-        <v>-6.0303065085876511E-17</v>
+        <v>-5.9966936159600695E-17</v>
       </c>
       <c r="AG23" s="12">
-        <v>-0.98479160288086642</v>
+        <v>-0.99028100482940951</v>
       </c>
       <c r="AH23" s="12">
-        <v>62.234408804787783</v>
+        <v>48.626705328383402</v>
       </c>
       <c r="AI23" s="7"/>
       <c r="AJ23" s="8"/>
@@ -3660,11 +3660,11 @@
       </c>
       <c r="C24" s="28" cm="1">
         <f t="array" ref="C24">DEGREES(C27)</f>
-        <v>10.000018723968342</v>
+        <v>-0.72998127603165697</v>
       </c>
       <c r="D24" s="28" cm="1">
         <f t="array" ref="D24">DEGREES(D27)</f>
-        <v>-3.0555237504089516E-2</v>
+        <v>-1.4994029875553573E-2</v>
       </c>
       <c r="E24" s="8"/>
       <c r="G24" s="8"/>
@@ -3676,10 +3676,10 @@
       <c r="M24" s="6"/>
       <c r="N24" s="33"/>
       <c r="O24" s="12">
-        <v>0.98480769626481723</v>
+        <v>0.88294743943796894</v>
       </c>
       <c r="P24" s="12">
-        <v>-0.1736484994970689</v>
+        <v>-0.46947185132863301</v>
       </c>
       <c r="Q24" s="12">
         <v>6.123233995736766E-17</v>
@@ -3700,16 +3700,16 @@
       <c r="AC24" s="6"/>
       <c r="AD24" s="33"/>
       <c r="AE24" s="12">
-        <v>6.0312441006962954E-17</v>
+        <v>2.2804347439796128E-17</v>
       </c>
       <c r="AF24" s="12">
         <v>-1</v>
       </c>
       <c r="AG24" s="12">
-        <v>5.0593848318912324E-17</v>
+        <v>6.3758254338625136E-17</v>
       </c>
       <c r="AH24" s="12">
-        <v>-1.3477965520860373E-14</v>
+        <v>-1.1846363450688617E-14</v>
       </c>
       <c r="AI24" s="7"/>
       <c r="AJ24" s="8"/>
@@ -3730,11 +3730,11 @@
       </c>
       <c r="C25" s="28" cm="1">
         <f t="array" ref="C25">DEGREES(C28)</f>
-        <v>6.3541887885436076E-15</v>
+        <v>7.0611218127027837E-15</v>
       </c>
       <c r="D25" s="28" cm="1">
         <f t="array" ref="D25">DEGREES(D28)</f>
-        <v>-79.994671222381413</v>
+        <v>-69.264671966748153</v>
       </c>
       <c r="E25" s="8"/>
       <c r="G25" s="6"/>
@@ -3743,11 +3743,11 @@
       </c>
       <c r="I25" s="12" cm="1">
         <f t="array" ref="I25">COS(L5)</f>
-        <v>1</v>
+        <v>0.95105651629515353</v>
       </c>
       <c r="J25" s="12" cm="1">
         <f t="array" ref="J25">-SIN(L5)</f>
-        <v>0</v>
+        <v>-0.3090169943749474</v>
       </c>
       <c r="K25" s="12">
         <v>0</v>
@@ -3759,10 +3759,10 @@
       <c r="M25" s="22"/>
       <c r="N25" s="33"/>
       <c r="O25" s="12">
-        <v>0.1736484994970689</v>
+        <v>0.46947185132863301</v>
       </c>
       <c r="P25" s="12">
-        <v>0.98480769626481723</v>
+        <v>0.88294743943796894</v>
       </c>
       <c r="Q25" s="12">
         <v>-6.123233995736766E-17</v>
@@ -3780,33 +3780,33 @@
       </c>
       <c r="Y25" s="12" cm="1">
         <f t="array" ref="Y25">COS(AB5)</f>
-        <v>-0.99999999570765619</v>
+        <v>-0.95108514374668696</v>
       </c>
       <c r="Z25" s="12" cm="1">
         <f t="array" ref="Z25">-SIN(AB5)*COS(Z5)</f>
-        <v>-5.673396100361585E-21</v>
+        <v>1.8916437850620962E-17</v>
       </c>
       <c r="AA25" s="12" cm="1">
         <f t="array" ref="AA25">SIN(AB5)*SIN(Z5)</f>
-        <v>9.2653589660490258E-5</v>
+        <v>-0.30892887424833548</v>
       </c>
       <c r="AB25" s="12" cm="1">
         <f t="array" ref="AB25">AA5*COS(AB5)</f>
-        <v>43.499999813283047</v>
+        <v>41.37220375298088</v>
       </c>
       <c r="AC25" s="22"/>
       <c r="AD25" s="33"/>
       <c r="AE25" s="12">
-        <v>-0.98479160288086642</v>
+        <v>-0.99028100482940951</v>
       </c>
       <c r="AF25" s="12">
-        <v>-5.0605023161579869E-17</v>
+        <v>-3.1450275453390291E-17</v>
       </c>
       <c r="AG25" s="12">
-        <v>0.17373974471989401</v>
+        <v>-0.13908102485262044</v>
       </c>
       <c r="AH25" s="12">
-        <v>330.60382005298482</v>
+        <v>330.8426090377464</v>
       </c>
       <c r="AI25" s="7"/>
       <c r="AJ25" s="8"/>
@@ -3827,7 +3827,7 @@
       </c>
       <c r="C26" s="28" cm="1">
         <f t="array" ref="C26">DEGREES(C29)</f>
-        <v>7.5726298296413201E-15</v>
+        <v>6.9717273078891572E-15</v>
       </c>
       <c r="D26" s="28" cm="1">
         <f t="array" ref="D26">DEGREES(D29)</f>
@@ -3838,11 +3838,11 @@
       <c r="H26" s="36"/>
       <c r="I26" s="12" cm="1">
         <f t="array" ref="I26">SIN(L5)*COS(J5)</f>
-        <v>0</v>
+        <v>0.3090169943749474</v>
       </c>
       <c r="J26" s="12" cm="1">
         <f t="array" ref="J26">COS(L5)*COS(J5)</f>
-        <v>1</v>
+        <v>0.95105651629515353</v>
       </c>
       <c r="K26" s="12" cm="1">
         <f t="array" ref="K26">-SIN(J5)</f>
@@ -3874,19 +3874,19 @@
       <c r="X26" s="36"/>
       <c r="Y26" s="12" cm="1">
         <f t="array" ref="Y26">SIN(AB5)</f>
-        <v>9.2653589660490258E-5</v>
+        <v>-0.30892887424833548</v>
       </c>
       <c r="Z26" s="12" cm="1">
         <f t="array" ref="Z26">COS(AB5)*COS(Z5)</f>
-        <v>-6.12323396945374E-17</v>
+        <v>-5.823716885029902E-17</v>
       </c>
       <c r="AA26" s="12" cm="1">
         <f t="array" ref="AA26">-COS(AB5)*SIN(Z5)</f>
-        <v>0.99999999570765619</v>
+        <v>0.95108514374668696</v>
       </c>
       <c r="AB26" s="12" cm="1">
         <f t="array" ref="AB26">AA5*SIN(AB5)</f>
-        <v>-4.0304311502313266E-3</v>
+        <v>13.438406029802593</v>
       </c>
       <c r="AC26" s="22"/>
       <c r="AD26" s="34"/>
@@ -3921,11 +3921,11 @@
       </c>
       <c r="C27" s="28">
         <f>ATAN2(Q49,P49)</f>
-        <v>0.17453325199432956</v>
+        <v>-1.274057674466198E-2</v>
       </c>
       <c r="D27" s="28" cm="1">
         <f t="array" ref="D27">ATAN2(AE41/COS(D28),AE42/COS(D28))</f>
-        <v>-5.3328949817521641E-4</v>
+        <v>-2.6169518947080547E-4</v>
       </c>
       <c r="E27" s="8"/>
       <c r="F27" s="8"/>
@@ -3999,11 +3999,11 @@
       </c>
       <c r="C28" s="28">
         <f>ATAN2((P49^2+Q49^2)^0.5,-O49)</f>
-        <v>1.109015156533957E-16</v>
+        <v>1.2323982451605394E-16</v>
       </c>
       <c r="D28" s="28" cm="1">
         <f t="array" ref="D28">ATAN2((AF43^2+AG43^2)^0.5,-AE43)</f>
-        <v>-1.3961703968809127</v>
+        <v>-1.2088965811335717</v>
       </c>
       <c r="E28" s="8"/>
       <c r="F28" s="8"/>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C29" s="28">
         <f>ATAN2(O47,O48)</f>
-        <v>1.3216732356197833E-16</v>
+        <v>1.2167959607386623E-16</v>
       </c>
       <c r="D29" s="28" cm="1">
         <f t="array" ref="D29">ATAN2(AF43/COS(D28),AE43/COS(D28))</f>
@@ -4089,16 +4089,16 @@
       </c>
       <c r="O29" s="12" cm="1">
         <f t="array" ref="O29:R32">MMULT(_xlfn.ANCHORARRAY(O23),I31:L34)</f>
-        <v>-4.9669175696028064E-17</v>
+        <v>-2.5318077775183396E-17</v>
       </c>
       <c r="P29" s="12">
         <v>-1</v>
       </c>
       <c r="Q29" s="12">
-        <v>1.3216732356197833E-16</v>
+        <v>1.440441377344903E-16</v>
       </c>
       <c r="R29" s="12">
-        <v>1.3640708143894156E-14</v>
+        <v>1.6794457082773388E-14</v>
       </c>
       <c r="S29" s="7"/>
       <c r="T29" s="8"/>
@@ -4116,16 +4116,16 @@
       </c>
       <c r="AE29" s="12" cm="1">
         <f t="array" ref="AE29:AH32">MMULT(_xlfn.ANCHORARRAY(AE23),Y31:AB34)</f>
-        <v>-0.17373974471989401</v>
+        <v>0.13908102485262044</v>
       </c>
       <c r="AF29" s="12">
-        <v>0.98479160288086642</v>
+        <v>0.99028100482940951</v>
       </c>
       <c r="AG29" s="12">
         <v>-1.2060415930063873E-16</v>
       </c>
       <c r="AH29" s="12">
-        <v>235.90240797282857</v>
+        <v>223.26276053004975</v>
       </c>
       <c r="AI29" s="7"/>
       <c r="AJ29" s="8"/>
@@ -4154,16 +4154,16 @@
       <c r="M30" s="6"/>
       <c r="N30" s="33"/>
       <c r="O30" s="12">
-        <v>0.98480769626481723</v>
+        <v>0.88294743943796894</v>
       </c>
       <c r="P30" s="12">
-        <v>-7.1865243911658964E-17</v>
+        <v>-8.9979199958337278E-17</v>
       </c>
       <c r="Q30" s="12">
-        <v>-0.1736484994970689</v>
+        <v>-0.46947185132863301</v>
       </c>
       <c r="R30" s="12">
-        <v>299.98160722887854</v>
+        <v>243.38223796141432</v>
       </c>
       <c r="S30" s="7"/>
       <c r="T30" s="8"/>
@@ -4178,16 +4178,16 @@
       <c r="AC30" s="6"/>
       <c r="AD30" s="33"/>
       <c r="AE30" s="12">
-        <v>6.0312441006962954E-17</v>
+        <v>2.2804347439796128E-17</v>
       </c>
       <c r="AF30" s="12">
-        <v>-1.1182618827627998E-16</v>
+        <v>-1.249905942959928E-16</v>
       </c>
       <c r="AG30" s="12">
         <v>-1</v>
       </c>
       <c r="AH30" s="12">
-        <v>-2.2400190671900561E-14</v>
+        <v>-2.3090131603305158E-14</v>
       </c>
       <c r="AI30" s="7"/>
       <c r="AJ30" s="8"/>
@@ -4229,16 +4229,16 @@
       <c r="M31" s="22"/>
       <c r="N31" s="33"/>
       <c r="O31" s="12">
-        <v>0.1736484994970689</v>
+        <v>0.46947185132863301</v>
       </c>
       <c r="P31" s="12">
-        <v>1.2153441960768702E-16</v>
+        <v>1.1529727773352067E-16</v>
       </c>
       <c r="Q31" s="12">
-        <v>0.98480769626481723</v>
+        <v>0.88294743943796894</v>
       </c>
       <c r="R31" s="12">
-        <v>235.90127687389543</v>
+        <v>230.80653638715378</v>
       </c>
       <c r="S31" s="7"/>
       <c r="T31" s="8"/>
@@ -4267,16 +4267,16 @@
       <c r="AC31" s="22"/>
       <c r="AD31" s="33"/>
       <c r="AE31" s="12">
-        <v>-0.98479160288086642</v>
+        <v>-0.99028100482940951</v>
       </c>
       <c r="AF31" s="12">
-        <v>-0.17373974471989401</v>
+        <v>0.13908102485262044</v>
       </c>
       <c r="AG31" s="12">
         <v>-3.9966532048785048E-17</v>
       </c>
       <c r="AH31" s="12">
-        <v>299.9648160716315</v>
+        <v>355.36954777050602</v>
       </c>
       <c r="AI31" s="7"/>
       <c r="AJ31" s="8"/>
@@ -4529,16 +4529,16 @@
       </c>
       <c r="O35" s="12" cm="1">
         <f t="array" ref="O35:R38">MMULT(_xlfn.ANCHORARRAY(O29),I37:L40)</f>
-        <v>-4.9669175696028064E-17</v>
+        <v>-6.2007484558686267E-17</v>
       </c>
       <c r="P35" s="12">
-        <v>7.0934983604610671E-17</v>
+        <v>6.0447256116498581E-17</v>
       </c>
       <c r="Q35" s="12">
         <v>1</v>
       </c>
       <c r="R35" s="12">
-        <v>1.3640708143894156E-14</v>
+        <v>1.6794457082773388E-14</v>
       </c>
       <c r="S35" s="7"/>
       <c r="T35" s="8"/>
@@ -4556,16 +4556,16 @@
       </c>
       <c r="AE35" s="12" cm="1">
         <f t="array" ref="AE35:AH38">MMULT(_xlfn.ANCHORARRAY(AE29),Y37:AB40)</f>
-        <v>-0.17373974471989401</v>
+        <v>-0.35405155184749815</v>
       </c>
       <c r="AF35" s="12">
-        <v>-6.0303065085876511E-17</v>
+        <v>-6.333808857683158E-17</v>
       </c>
       <c r="AG35" s="12">
-        <v>-0.98479160288086642</v>
+        <v>-0.93522590780750858</v>
       </c>
       <c r="AH35" s="12">
-        <v>235.90240797282857</v>
+        <v>223.26276053004975</v>
       </c>
       <c r="AI35" s="7"/>
       <c r="AJ35" s="8"/>
@@ -4595,16 +4595,16 @@
       <c r="M36" s="6"/>
       <c r="N36" s="33"/>
       <c r="O36" s="12">
-        <v>0.98480769626481723</v>
+        <v>0.99991883994995601</v>
       </c>
       <c r="P36" s="12">
-        <v>-0.1736484994970689</v>
+        <v>1.2740232067514956E-2</v>
       </c>
       <c r="Q36" s="12">
         <v>6.1232339957367648E-17</v>
       </c>
       <c r="R36" s="12">
-        <v>299.98160722887854</v>
+        <v>243.38223796141432</v>
       </c>
       <c r="S36" s="7"/>
       <c r="T36" s="8"/>
@@ -4619,16 +4619,16 @@
       <c r="AC36" s="6"/>
       <c r="AD36" s="33"/>
       <c r="AE36" s="12">
-        <v>6.0312441006962954E-17</v>
+        <v>8.0077825976896905E-17</v>
       </c>
       <c r="AF36" s="12">
         <v>-1</v>
       </c>
       <c r="AG36" s="12">
-        <v>5.0593848318912324E-17</v>
+        <v>3.7409581716098431E-17</v>
       </c>
       <c r="AH36" s="12">
-        <v>-2.2400190671900561E-14</v>
+        <v>-2.3090131603305158E-14</v>
       </c>
       <c r="AI36" s="7"/>
       <c r="AJ36" s="8"/>
@@ -4655,11 +4655,11 @@
       </c>
       <c r="I37" s="12" cm="1">
         <f t="array" ref="I37">COS(L7)</f>
-        <v>1</v>
+        <v>0.8768945990445054</v>
       </c>
       <c r="J37" s="12" cm="1">
         <f t="array" ref="J37">-SIN(L7)</f>
-        <v>0</v>
+        <v>0.4806827042515428</v>
       </c>
       <c r="K37" s="12">
         <v>0</v>
@@ -4671,16 +4671,16 @@
       <c r="M37" s="22"/>
       <c r="N37" s="33"/>
       <c r="O37" s="12">
-        <v>0.1736484994970689</v>
+        <v>-1.2740232067514956E-2</v>
       </c>
       <c r="P37" s="12">
-        <v>0.98480769626481723</v>
+        <v>0.99991883994995601</v>
       </c>
       <c r="Q37" s="12">
-        <v>-6.1232339957367648E-17</v>
+        <v>-6.123233995736766E-17</v>
       </c>
       <c r="R37" s="12">
-        <v>235.90127687389543</v>
+        <v>230.80653638715378</v>
       </c>
       <c r="S37" s="7"/>
       <c r="T37" s="8"/>
@@ -4692,15 +4692,15 @@
       </c>
       <c r="Y37" s="12" cm="1">
         <f t="array" ref="Y37">COS(AB7)</f>
-        <v>1</v>
+        <v>0.8768945990445054</v>
       </c>
       <c r="Z37" s="12" cm="1">
         <f t="array" ref="Z37">-SIN(AB7)*COS(Z7)</f>
-        <v>0</v>
+        <v>2.9433326758357286E-17</v>
       </c>
       <c r="AA37" s="12" cm="1">
         <f t="array" ref="AA37">SIN(AB7)*SIN(Z7)</f>
-        <v>0</v>
+        <v>-0.4806827042515428</v>
       </c>
       <c r="AB37" s="12" cm="1">
         <f t="array" ref="AB37">AA7*COS(AB7)</f>
@@ -4709,16 +4709,16 @@
       <c r="AC37" s="22"/>
       <c r="AD37" s="33"/>
       <c r="AE37" s="12">
-        <v>-0.98479160288086642</v>
+        <v>-0.93522590780750858</v>
       </c>
       <c r="AF37" s="12">
-        <v>-5.0605023161579869E-17</v>
+        <v>-6.1645937033944643E-17</v>
       </c>
       <c r="AG37" s="12">
-        <v>0.17373974471989401</v>
+        <v>0.35405155184749815</v>
       </c>
       <c r="AH37" s="12">
-        <v>299.9648160716315</v>
+        <v>355.36954777050602</v>
       </c>
       <c r="AI37" s="7"/>
       <c r="AJ37" s="8"/>
@@ -4743,11 +4743,11 @@
       <c r="H38" s="36"/>
       <c r="I38" s="12" cm="1">
         <f t="array" ref="I38">SIN(L7)*COS(J7)</f>
-        <v>0</v>
+        <v>-2.9433326758357286E-17</v>
       </c>
       <c r="J38" s="12" cm="1">
         <f t="array" ref="J38">COS(L7)*COS(J7)</f>
-        <v>6.123233995736766E-17</v>
+        <v>5.3694308195472764E-17</v>
       </c>
       <c r="K38" s="12" cm="1">
         <f t="array" ref="K38">-SIN(J7)</f>
@@ -4779,15 +4779,15 @@
       <c r="X38" s="36"/>
       <c r="Y38" s="12" cm="1">
         <f t="array" ref="Y38">SIN(AB7)</f>
-        <v>0</v>
+        <v>-0.4806827042515428</v>
       </c>
       <c r="Z38" s="12" cm="1">
         <f t="array" ref="Z38">COS(AB7)*COS(Z7)</f>
-        <v>6.123233995736766E-17</v>
+        <v>5.3694308195472764E-17</v>
       </c>
       <c r="AA38" s="12" cm="1">
         <f t="array" ref="AA38">-COS(AB7)*SIN(Z7)</f>
-        <v>-1</v>
+        <v>-0.8768945990445054</v>
       </c>
       <c r="AB38" s="12" cm="1">
         <f t="array" ref="AB38">AA7*SIN(AB7)</f>
@@ -4830,11 +4830,11 @@
       <c r="H39" s="36"/>
       <c r="I39" s="12" cm="1">
         <f t="array" ref="I39">SIN(L7)*SIN(J7)</f>
-        <v>0</v>
+        <v>-0.4806827042515428</v>
       </c>
       <c r="J39" s="12" cm="1">
         <f t="array" ref="J39">COS(L7)*SIN(J7)</f>
-        <v>1</v>
+        <v>0.8768945990445054</v>
       </c>
       <c r="K39" s="12" cm="1">
         <f t="array" ref="K39">COS(J7)</f>
@@ -4971,16 +4971,16 @@
       </c>
       <c r="O41" s="12" cm="1">
         <f t="array" ref="O41:R44">MMULT(_xlfn.ANCHORARRAY(O35),I43:L46)</f>
-        <v>-4.9669175696028064E-17</v>
+        <v>-6.2007484558686267E-17</v>
       </c>
       <c r="P41" s="12">
         <v>-1</v>
       </c>
       <c r="Q41" s="12">
-        <v>1.3216732356197833E-16</v>
+        <v>1.2167959607386625E-16</v>
       </c>
       <c r="R41" s="12">
-        <v>1.3640708143894156E-14</v>
+        <v>1.6794457082773388E-14</v>
       </c>
       <c r="S41" s="7"/>
       <c r="T41" s="8"/>
@@ -4998,16 +4998,16 @@
       </c>
       <c r="AE41" s="12" cm="1">
         <f t="array" ref="AE41:AH44">MMULT(_xlfn.ANCHORARRAY(AE35),Y43:AB46)</f>
-        <v>0.1737397439741433</v>
+        <v>0.35405155032778718</v>
       </c>
       <c r="AF41" s="12">
-        <v>-1.6097611015176289E-5</v>
+        <v>-3.2804147203715756E-5</v>
       </c>
       <c r="AG41" s="12">
-        <v>0.98479160288086642</v>
+        <v>0.93522590780750858</v>
       </c>
       <c r="AH41" s="12">
-        <v>334.38156826091523</v>
+        <v>316.78535131080059</v>
       </c>
       <c r="AI41" s="7"/>
       <c r="AJ41" s="8"/>
@@ -5037,16 +5037,16 @@
       <c r="M42" s="6"/>
       <c r="N42" s="33"/>
       <c r="O42" s="12">
-        <v>0.98480769626481723</v>
+        <v>0.99991883994995601</v>
       </c>
       <c r="P42" s="12">
-        <v>-7.1865243911658964E-17</v>
+        <v>-6.0452225736273818E-17</v>
       </c>
       <c r="Q42" s="12">
-        <v>-0.1736484994970689</v>
+        <v>1.2740232067514956E-2</v>
       </c>
       <c r="R42" s="12">
-        <v>299.98160722887854</v>
+        <v>243.38223796141432</v>
       </c>
       <c r="S42" s="7"/>
       <c r="T42" s="8"/>
@@ -5061,16 +5061,16 @@
       <c r="AC42" s="6"/>
       <c r="AD42" s="33"/>
       <c r="AE42" s="12">
-        <v>-9.2653589660550567E-5</v>
+        <v>-9.265358966057034E-5</v>
       </c>
       <c r="AF42" s="12">
         <v>-0.99999999570765619</v>
       </c>
       <c r="AG42" s="12">
-        <v>-1.7305852770798714E-16</v>
+        <v>-1.5987426110517322E-16</v>
       </c>
       <c r="AH42" s="12">
-        <v>-2.7459575503791794E-14</v>
+        <v>-2.6831089774915E-14</v>
       </c>
       <c r="AI42" s="7"/>
       <c r="AJ42" s="8"/>
@@ -5113,16 +5113,16 @@
       <c r="M43" s="22"/>
       <c r="N43" s="33"/>
       <c r="O43" s="12">
-        <v>0.1736484994970689</v>
+        <v>-1.2740232067514956E-2</v>
       </c>
       <c r="P43" s="12">
-        <v>1.2153441960768702E-16</v>
+        <v>1.2245971029496007E-16</v>
       </c>
       <c r="Q43" s="12">
-        <v>0.98480769626481723</v>
+        <v>0.99991883994995601</v>
       </c>
       <c r="R43" s="12">
-        <v>235.90127687389543</v>
+        <v>230.80653638715378</v>
       </c>
       <c r="S43" s="7"/>
       <c r="T43" s="8"/>
@@ -5151,16 +5151,16 @@
       <c r="AC43" s="22"/>
       <c r="AD43" s="33"/>
       <c r="AE43" s="12">
-        <v>0.98479159865380228</v>
+        <v>0.93522590379319748</v>
       </c>
       <c r="AF43" s="12">
-        <v>-9.1244477074449602E-5</v>
+        <v>-8.665203750187469E-5</v>
       </c>
       <c r="AG43" s="12">
-        <v>-0.17373974471989401</v>
+        <v>-0.35405155184749815</v>
       </c>
       <c r="AH43" s="12">
-        <v>282.59084159964209</v>
+        <v>319.96439258575617</v>
       </c>
       <c r="AI43" s="7"/>
       <c r="AJ43" s="8"/>
@@ -5416,13 +5416,13 @@
         <v>1</v>
       </c>
       <c r="P47" s="12">
-        <v>-1.1090151565339572E-16</v>
+        <v>-1.2323982451605394E-16</v>
       </c>
       <c r="Q47" s="12">
-        <v>1.3216732356197833E-16</v>
+        <v>1.2167959607386625E-16</v>
       </c>
       <c r="R47" s="12">
-        <v>2.6857440500091989E-14</v>
+        <v>2.8962416690160015E-14</v>
       </c>
       <c r="S47" s="7"/>
       <c r="T47" s="8"/>
@@ -5468,16 +5468,16 @@
       <c r="M48" s="6"/>
       <c r="N48" s="33"/>
       <c r="O48" s="12">
-        <v>1.3216732356197833E-16</v>
+        <v>1.2167959607386623E-16</v>
       </c>
       <c r="P48" s="12">
-        <v>0.98480769626481723</v>
+        <v>0.99991883994995601</v>
       </c>
       <c r="Q48" s="12">
-        <v>-0.1736484994970689</v>
+        <v>1.2740232067514956E-2</v>
       </c>
       <c r="R48" s="12">
-        <v>282.61675727917168</v>
+        <v>244.65626116816583</v>
       </c>
       <c r="S48" s="7"/>
       <c r="T48" s="8"/>
@@ -5536,16 +5536,16 @@
       <c r="M49" s="22"/>
       <c r="N49" s="33"/>
       <c r="O49" s="12">
-        <v>-1.109015156533957E-16</v>
+        <v>-1.2323982451605391E-16</v>
       </c>
       <c r="P49" s="12">
-        <v>0.1736484994970689</v>
+        <v>-1.2740232067514956E-2</v>
       </c>
       <c r="Q49" s="12">
-        <v>0.98480769626481723</v>
+        <v>0.99991883994995601</v>
       </c>
       <c r="R49" s="12">
-        <v>334.38204650037716</v>
+        <v>330.7984203821494</v>
       </c>
       <c r="S49" s="7"/>
       <c r="T49" s="8"/>
